--- a/1. List_ManualData.xlsx
+++ b/1. List_ManualData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390E81BB-E20A-8F43-87ED-D78A8317C4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1461D4F-715B-7E4C-94DE-6FD1AAC4E1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="100" windowWidth="25440" windowHeight="13540" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -636,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
   </sheetData>

--- a/1. List_ManualData.xlsx
+++ b/1. List_ManualData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1461D4F-715B-7E4C-94DE-6FD1AAC4E1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A8B628-4F78-7947-B144-0AB70DAABA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="100" windowWidth="25440" windowHeight="13540" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -636,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>4.3999999999999997E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
   </sheetData>

--- a/1. List_ManualData.xlsx
+++ b/1. List_ManualData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A8B628-4F78-7947-B144-0AB70DAABA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B10046-D256-EB47-87BD-C2E270B519A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="100" windowWidth="25440" windowHeight="13540" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -574,14 +574,14 @@
       <c r="C4" s="4">
         <v>26.47</v>
       </c>
-      <c r="D4" s="4">
-        <v>1.08</v>
+      <c r="D4" s="5">
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="E4" s="4">
         <v>23.69</v>
       </c>
-      <c r="F4" s="4">
-        <v>1.32</v>
+      <c r="F4" s="5">
+        <v>1.32E-2</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
@@ -591,14 +591,14 @@
       <c r="C5" s="4">
         <v>24.16</v>
       </c>
-      <c r="D5" s="4">
-        <v>1.69</v>
+      <c r="D5" s="5">
+        <v>1.6899999999999998E-2</v>
       </c>
       <c r="E5" s="4">
         <v>23.54</v>
       </c>
-      <c r="F5" s="4">
-        <v>1.71</v>
+      <c r="F5" s="5">
+        <v>1.7100000000000001E-2</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.2">
@@ -608,14 +608,14 @@
       <c r="C6" s="4">
         <v>35.590000000000003</v>
       </c>
-      <c r="D6" s="4">
-        <v>0.57999999999999996</v>
+      <c r="D6" s="5">
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="E6" s="4">
         <v>31.25</v>
       </c>
-      <c r="F6" s="4">
-        <v>0.76</v>
+      <c r="F6" s="5">
+        <v>7.6E-3</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
